--- a/config/cross/online_fight/theme.xlsx
+++ b/config/cross/online_fight/theme.xlsx
@@ -1183,7 +1183,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>開始時覚醒値MAX</t>
+          <t>开始时唤醒值MAX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>通常スキル消費なし</t>
+          <t>通常不消耗技能</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>覚醒値高速回復</t>
+          <t>觉醒值快速回复</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>HP回復効果低下</t>
+          <t>HP回复效果低下</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>A以下の仲間限定</t>
+          <t>限定A以下的伙伴</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>S以下の仲間限定</t>
+          <t>限定S以下的伙伴</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>出陣S仲間2体まで</t>
+          <t>出阵S最多2名伙伴</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
